--- a/待规划小区/cell-tree-export.xlsx
+++ b/待规划小区/cell-tree-export.xlsx
@@ -11,7 +11,7 @@
     <sheet name="NR" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LTE!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LTE!$A$1:$D$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -672,10 +672,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1060,8 +1064,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="3.8" customWidth="1"/>
     <col min="3" max="3" width="9.4" customWidth="1"/>
@@ -1083,49 +1087,91 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>460</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <v>11</v>
       </c>
       <c r="C2" s="2">
-        <v>111111</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1</v>
+        <v>936521</v>
+      </c>
+      <c r="D2" s="3">
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="3">
+      <c r="A3" s="4">
         <v>460</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>111111</v>
-      </c>
-      <c r="D3" s="2">
-        <v>2</v>
+        <v>542654</v>
+      </c>
+      <c r="D3" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="3">
+      <c r="A4" s="5">
         <v>460</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="5">
         <v>11</v>
       </c>
       <c r="C4" s="2">
-        <v>111111</v>
-      </c>
-      <c r="D4" s="2">
-        <v>3</v>
+        <v>542654</v>
+      </c>
+      <c r="D4" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="5">
+        <v>460</v>
+      </c>
+      <c r="B5" s="5">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2">
+        <v>542654</v>
+      </c>
+      <c r="D5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5">
+        <v>460</v>
+      </c>
+      <c r="B6" s="5">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2">
+        <v>542654</v>
+      </c>
+      <c r="D6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="5">
+        <v>460</v>
+      </c>
+      <c r="B7" s="5">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2">
+        <v>542654</v>
+      </c>
+      <c r="D7">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D1" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D4" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1139,8 +1185,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="40.2083333333333" customWidth="1"/>
   </cols>
@@ -1167,9 +1213,9 @@
         <v>11</v>
       </c>
       <c r="C2" s="2">
-        <v>1111111</v>
-      </c>
-      <c r="D2" s="2">
+        <v>7906572</v>
+      </c>
+      <c r="D2" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1181,66 +1227,24 @@
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>1111111</v>
-      </c>
-      <c r="D3" s="2">
+        <v>7906572</v>
+      </c>
+      <c r="D3" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="3">
+      <c r="A4">
         <v>460</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>11</v>
       </c>
       <c r="C4" s="2">
-        <v>1111111</v>
-      </c>
-      <c r="D4" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="3">
-        <v>460</v>
-      </c>
-      <c r="B5" s="3">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2222222</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="3">
-        <v>460</v>
-      </c>
-      <c r="B6" s="3">
-        <v>11</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2222222</v>
-      </c>
-      <c r="D6" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="3">
-        <v>460</v>
-      </c>
-      <c r="B7" s="3">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2222222</v>
-      </c>
-      <c r="D7" s="2">
-        <v>3</v>
+        <v>7905713</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
